--- a/02_DONNEES_NORMALISEES/menages/M04_MENAGES_PowerQuery.xlsx
+++ b/02_DONNEES_NORMALISEES/menages/M04_MENAGES_PowerQuery.xlsx
@@ -563,7 +563,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -625,15 +625,20 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Valeur non listee. Verifier l'orthographe ou completer le referentiel." promptTitle="Liste" prompt="Intervenant (PARAM_TAUX_INTERVENANTS)" type="list" errorStyle="warning">
+      <formula1>=PARAM_TAUX_INTERVENANTS!$B$2:$B$6</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -862,13 +867,13 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -946,7 +951,7 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>

--- a/02_DONNEES_NORMALISEES/menages/M04_MENAGES_PowerQuery.xlsx
+++ b/02_DONNEES_NORMALISEES/menages/M04_MENAGES_PowerQuery.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SOURCE_RAW" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PARAM_TAUX_INTERVENANTS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PARAMETRES_M04" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="MASTER" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="VUE_ACTIVE" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="VUE_ECART_HOSTAWAY" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="POWER_QUERY_CODE" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="README" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOURCE_RAW" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PARAM_TAUX_INTERVENANTS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PARAMETRES_M04" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MASTER" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VUE_ACTIVE" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VUE_ECART_HOSTAWAY" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="POWER_QUERY_CODE" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -232,7 +232,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tbl_SOURCE_RAW" displayName="tbl_SOURCE_RAW" ref="A1:G2" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tbl_SOURCE_RAW" displayName="tbl_SOURCE_RAW" ref="A1:G21" headerRowCount="1">
   <autoFilter ref="A1:G2"/>
   <tableColumns count="7">
     <tableColumn id="1" name="mois_saisie"/>
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -618,9 +618,734 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>← Coller ici les données du Google Sheet 'Suivi ménage'. Vérifier que les noms de colonnes correspondent exactement.</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>T3 - 18 cugnaux (David)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Import Google Sheet Suivi menage; lavage=40</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Studio - 76 (Dureuil)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Import Google Sheet Suivi menage; lavage=13</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Studio - St Pierre (florane)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Import Google Sheet Suivi menage; lavage=17</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Studio - 96 (Florane)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Kira</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Import Google Sheet Suivi menage; lavage=70</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Studio - 46 (Didier )</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Kira</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Import Google Sheet Suivi menage; lavage=64</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Studio - 96 (Florane)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Kira</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Import Google Sheet Suivi menage; lavage=60</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Studio - 97 (Maryline)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Kira</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Import Google Sheet Suivi menage; lavage=50</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Studio - 76 (Dureuil)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Kira</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Import Google Sheet Suivi menage; lavage=10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Studio - 46 (Didier )</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Kira</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Import Google Sheet Suivi menage; lavage=80</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Studio - Puits vert (Caroline)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Import Google Sheet Suivi menage; lavage=10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Studio - St Pierre (florane)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Import Google Sheet Suivi menage; lavage=8</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Studio - 76 (Dureuil)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Import Google Sheet Suivi menage; lavage=25</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>T3 - 18 cugnaux (David)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Import Google Sheet Suivi menage; lavage=51</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Studio - 97 (Maryline)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Kira</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Import Google Sheet Suivi menage; lavage=40</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Studio - 46 (Didier )</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Kira</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Import Google Sheet Suivi menage; lavage=90</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Studio - 96 (Florane)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Kira</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Import Google Sheet Suivi menage; lavage=60</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Studio - 76 (Dureuil)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Import Google Sheet Suivi menage; lavage=72</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>T3 - 18 cugnaux (David)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>17.5</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Import Google Sheet Suivi menage; lavage=45</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>T3 - 18 cugnaux (David)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Kira</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Import Google Sheet Suivi menage; lavage=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>T2 - 65 (Gabriel)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Kira</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Import Google Sheet Suivi menage; lavage=0</t>
         </is>
       </c>
     </row>

--- a/02_DONNEES_NORMALISEES/menages/M04_MENAGES_PowerQuery.xlsx
+++ b/02_DONNEES_NORMALISEES/menages/M04_MENAGES_PowerQuery.xlsx
@@ -638,19 +638,15 @@
           <t>MENAGE_STANDARD</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>20</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Import Google Sheet Suivi menage; lavage=40</t>
+          <t>lavage=40.0; import lot6b</t>
         </is>
       </c>
     </row>
@@ -675,19 +671,15 @@
           <t>MENAGE_STANDARD</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Import Google Sheet Suivi menage; lavage=13</t>
+          <t>lavage=13.0; import lot6b</t>
         </is>
       </c>
     </row>
@@ -712,19 +704,15 @@
           <t>MENAGE_STANDARD</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Import Google Sheet Suivi menage; lavage=17</t>
+          <t>lavage=17.0; import lot6b</t>
         </is>
       </c>
     </row>
@@ -749,19 +737,15 @@
           <t>MENAGE_STANDARD</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>24</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Import Google Sheet Suivi menage; lavage=70</t>
+          <t>lavage=70.0; import lot6b</t>
         </is>
       </c>
     </row>
@@ -786,19 +770,15 @@
           <t>MENAGE_STANDARD</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="E6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>25</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Import Google Sheet Suivi menage; lavage=64</t>
+          <t>lavage=64.0; import lot6b</t>
         </is>
       </c>
     </row>
@@ -823,19 +803,15 @@
           <t>MENAGE_STANDARD</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>18</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Import Google Sheet Suivi menage; lavage=60</t>
+          <t>lavage=60.0; import lot6b</t>
         </is>
       </c>
     </row>
@@ -860,19 +836,15 @@
           <t>MENAGE_STANDARD</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>15</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Import Google Sheet Suivi menage; lavage=50</t>
+          <t>lavage=50.0; import lot6b</t>
         </is>
       </c>
     </row>
@@ -897,19 +869,15 @@
           <t>MENAGE_STANDARD</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Import Google Sheet Suivi menage; lavage=10</t>
+          <t>lavage=10.0; import lot6b</t>
         </is>
       </c>
     </row>
@@ -934,19 +902,15 @@
           <t>MENAGE_STANDARD</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="E10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" t="n">
+        <v>28</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Import Google Sheet Suivi menage; lavage=80</t>
+          <t>lavage=80.0; import lot6b</t>
         </is>
       </c>
     </row>
@@ -971,19 +935,15 @@
           <t>MENAGE_STANDARD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Import Google Sheet Suivi menage; lavage=10</t>
+          <t>lavage=10.0; import lot6b</t>
         </is>
       </c>
     </row>
@@ -1008,19 +968,15 @@
           <t>MENAGE_STANDARD</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Import Google Sheet Suivi menage; lavage=8</t>
+          <t>lavage=8.0; import lot6b</t>
         </is>
       </c>
     </row>
@@ -1045,19 +1001,15 @@
           <t>MENAGE_STANDARD</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Import Google Sheet Suivi menage; lavage=25</t>
+          <t>lavage=25.0; import lot6b</t>
         </is>
       </c>
     </row>
@@ -1082,19 +1034,15 @@
           <t>MENAGE_STANDARD</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="E14" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" t="n">
+        <v>26</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Import Google Sheet Suivi menage; lavage=51</t>
+          <t>lavage=51.0; import lot6b</t>
         </is>
       </c>
     </row>
@@ -1119,19 +1067,15 @@
           <t>MENAGE_STANDARD</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>11</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Import Google Sheet Suivi menage; lavage=40</t>
+          <t>lavage=40.0; import lot6b</t>
         </is>
       </c>
     </row>
@@ -1156,19 +1100,15 @@
           <t>MENAGE_STANDARD</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="E16" t="n">
+        <v>9</v>
+      </c>
+      <c r="F16" t="n">
+        <v>31</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Import Google Sheet Suivi menage; lavage=90</t>
+          <t>lavage=90.0; import lot6b</t>
         </is>
       </c>
     </row>
@@ -1193,19 +1133,15 @@
           <t>MENAGE_STANDARD</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>16</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Import Google Sheet Suivi menage; lavage=60</t>
+          <t>lavage=60.0; import lot6b</t>
         </is>
       </c>
     </row>
@@ -1230,19 +1166,15 @@
           <t>MENAGE_STANDARD</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="E18" t="n">
+        <v>9</v>
+      </c>
+      <c r="F18" t="n">
+        <v>21</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Import Google Sheet Suivi menage; lavage=72</t>
+          <t>lavage=72.0; import lot6b</t>
         </is>
       </c>
     </row>
@@ -1267,19 +1199,15 @@
           <t>MENAGE_STANDARD</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>17.5</t>
-        </is>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>17.5</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Import Google Sheet Suivi menage; lavage=45</t>
+          <t>lavage=45.0; import lot6b</t>
         </is>
       </c>
     </row>
@@ -1304,15 +1232,12 @@
           <t>MENAGE_STANDARD</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Import Google Sheet Suivi menage; lavage=0</t>
+          <t>lavage=0; import lot6b</t>
         </is>
       </c>
     </row>
@@ -1337,15 +1262,12 @@
           <t>MENAGE_STANDARD</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Import Google Sheet Suivi menage; lavage=0</t>
+          <t>lavage=0; import lot6b</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1899,9 +1821,2912 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>← Alimenté par Power Query (Q7_MASTER) après collage des données dans SOURCE_RAW.</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MEN-2026-03-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>412a76157796c535</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>LOG_0008</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>480140</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>T3 - 18 cugnaux (David)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>INT_0001</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>6</v>
+      </c>
+      <c r="O2" t="n">
+        <v>20</v>
+      </c>
+      <c r="P2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>200</v>
+      </c>
+      <c r="R2" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="S2" t="n">
+        <v>55</v>
+      </c>
+      <c r="T2" t="n">
+        <v>330</v>
+      </c>
+      <c r="U2" t="n">
+        <v>130</v>
+      </c>
+      <c r="V2" t="n">
+        <v>200</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>MEN-2026-03-001</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MEN-2026-03-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>10fe24845310699b</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>LOG_0014</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>PROP_0010</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>481998</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Studio - 76 (Dureuil)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>INT_0001</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>60</v>
+      </c>
+      <c r="R3" t="n">
+        <v>20</v>
+      </c>
+      <c r="S3" t="n">
+        <v>29</v>
+      </c>
+      <c r="T3" t="n">
+        <v>87</v>
+      </c>
+      <c r="U3" t="n">
+        <v>27</v>
+      </c>
+      <c r="V3" t="n">
+        <v>60</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>MEN-2026-03-002</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MEN-2026-03-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>cd99c4ebea0ad575</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>LOG_0010</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>480142</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Studio - St Pierre (florane)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>INT_0001</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>8</v>
+      </c>
+      <c r="P4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>80</v>
+      </c>
+      <c r="R4" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="S4" t="n">
+        <v>29</v>
+      </c>
+      <c r="T4" t="n">
+        <v>87</v>
+      </c>
+      <c r="U4" t="n">
+        <v>7</v>
+      </c>
+      <c r="V4" t="n">
+        <v>80</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>MEN-2026-03-003</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MEN-2026-03-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>fdc6efca63ff5d45</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>LOG_0005</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>493047</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Studio - 96 (Florane)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>INT_0002</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Kheira</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>8</v>
+      </c>
+      <c r="O5" t="n">
+        <v>24</v>
+      </c>
+      <c r="P5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>240</v>
+      </c>
+      <c r="R5" t="n">
+        <v>30</v>
+      </c>
+      <c r="S5" t="n">
+        <v>29</v>
+      </c>
+      <c r="T5" t="n">
+        <v>232</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-8</v>
+      </c>
+      <c r="V5" t="n">
+        <v>240</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>MEN-2026-03-004</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MEN-2026-03-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>67ea9a859d63810e</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>LOG_0001</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PROP_0001</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>482204</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Studio - 46 (Didier )</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>INT_0002</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Kheira</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>25</v>
+      </c>
+      <c r="P6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>250</v>
+      </c>
+      <c r="R6" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="S6" t="n">
+        <v>29</v>
+      </c>
+      <c r="T6" t="n">
+        <v>232</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-18</v>
+      </c>
+      <c r="V6" t="n">
+        <v>250</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>MEN-2026-03-005</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-001</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>86d918eabec2ad65</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>LOG_0005</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>493047</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Studio - 96 (Florane)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>INT_0002</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Kheira</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>18</v>
+      </c>
+      <c r="P7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>180</v>
+      </c>
+      <c r="R7" t="n">
+        <v>30</v>
+      </c>
+      <c r="S7" t="n">
+        <v>29</v>
+      </c>
+      <c r="T7" t="n">
+        <v>174</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="V7" t="n">
+        <v>180</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-001</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-002</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>cb042425a5d3261c</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>LOG_0015</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>PROP_0011</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>482378</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Studio - 97 (Maryline)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>INT_0002</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Kheira</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>15</v>
+      </c>
+      <c r="P8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>150</v>
+      </c>
+      <c r="R8" t="n">
+        <v>30</v>
+      </c>
+      <c r="S8" t="n">
+        <v>29</v>
+      </c>
+      <c r="T8" t="n">
+        <v>145</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>150</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-002</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-003</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>70877dd74a01ae66</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>LOG_0014</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>PROP_0010</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>481998</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Studio - 76 (Dureuil)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>INT_0002</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Kheira</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>30</v>
+      </c>
+      <c r="R9" t="n">
+        <v>30</v>
+      </c>
+      <c r="S9" t="n">
+        <v>29</v>
+      </c>
+      <c r="T9" t="n">
+        <v>29</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>30</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-003</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-004</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3f65a1e12ee25da3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>LOG_0001</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>PROP_0001</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>482204</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Studio - 46 (Didier )</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>INT_0002</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Kheira</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>8</v>
+      </c>
+      <c r="O10" t="n">
+        <v>28</v>
+      </c>
+      <c r="P10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>280</v>
+      </c>
+      <c r="R10" t="n">
+        <v>35</v>
+      </c>
+      <c r="S10" t="n">
+        <v>29</v>
+      </c>
+      <c r="T10" t="n">
+        <v>232</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-48</v>
+      </c>
+      <c r="V10" t="n">
+        <v>280</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-004</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-005</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>df44e2430ab62ba1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>LOG_0006</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PROP_0006</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>487144</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Studio - Puits vert (Caroline)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>INT_0001</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>30</v>
+      </c>
+      <c r="R11" t="n">
+        <v>30</v>
+      </c>
+      <c r="S11" t="n">
+        <v>29</v>
+      </c>
+      <c r="T11" t="n">
+        <v>29</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>30</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-005</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-006</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>34d6b9535638fb15</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>LOG_0010</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>480142</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Studio - St Pierre (florane)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>INT_0001</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>40</v>
+      </c>
+      <c r="R12" t="n">
+        <v>40</v>
+      </c>
+      <c r="S12" t="n">
+        <v>29</v>
+      </c>
+      <c r="T12" t="n">
+        <v>29</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-11</v>
+      </c>
+      <c r="V12" t="n">
+        <v>40</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-006</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-007</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>042de8d6d554973f</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>LOG_0014</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>PROP_0010</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>481998</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Studio - 76 (Dureuil)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>INT_0001</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>9</v>
+      </c>
+      <c r="P13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>90</v>
+      </c>
+      <c r="R13" t="n">
+        <v>30</v>
+      </c>
+      <c r="S13" t="n">
+        <v>29</v>
+      </c>
+      <c r="T13" t="n">
+        <v>87</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="V13" t="n">
+        <v>90</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-007</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-008</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>c73eb58dc740ec04</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>LOG_0008</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>480140</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>T3 - 18 cugnaux (David)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>INT_0001</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>26</v>
+      </c>
+      <c r="P14" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>260</v>
+      </c>
+      <c r="R14" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="S14" t="n">
+        <v>55</v>
+      </c>
+      <c r="T14" t="n">
+        <v>385</v>
+      </c>
+      <c r="U14" t="n">
+        <v>125</v>
+      </c>
+      <c r="V14" t="n">
+        <v>260</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-008</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MEN-2026-05-001</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7bd60d4dec036460</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>LOG_0015</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>PROP_0011</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>482378</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Studio - 97 (Maryline)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>INT_0002</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Kheira</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>4</v>
+      </c>
+      <c r="O15" t="n">
+        <v>11</v>
+      </c>
+      <c r="P15" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>110</v>
+      </c>
+      <c r="R15" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>29</v>
+      </c>
+      <c r="T15" t="n">
+        <v>116</v>
+      </c>
+      <c r="U15" t="n">
+        <v>6</v>
+      </c>
+      <c r="V15" t="n">
+        <v>110</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>MEN-2026-05-001</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MEN-2026-05-002</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>fd2b6b839bff2bc2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>LOG_0001</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>PROP_0001</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>482204</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Studio - 46 (Didier )</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>INT_0002</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Kheira</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>9</v>
+      </c>
+      <c r="O16" t="n">
+        <v>31</v>
+      </c>
+      <c r="P16" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>310</v>
+      </c>
+      <c r="R16" t="n">
+        <v>34.44</v>
+      </c>
+      <c r="S16" t="n">
+        <v>29</v>
+      </c>
+      <c r="T16" t="n">
+        <v>261</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-49</v>
+      </c>
+      <c r="V16" t="n">
+        <v>310</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>MEN-2026-05-002</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MEN-2026-05-003</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>503757d156fb07a0</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>LOG_0005</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>493047</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Studio - 96 (Florane)</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>INT_0002</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Kheira</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>16</v>
+      </c>
+      <c r="P17" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>160</v>
+      </c>
+      <c r="R17" t="n">
+        <v>32</v>
+      </c>
+      <c r="S17" t="n">
+        <v>29</v>
+      </c>
+      <c r="T17" t="n">
+        <v>145</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-15</v>
+      </c>
+      <c r="V17" t="n">
+        <v>160</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>MEN-2026-05-003</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MEN-2026-05-004</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2ffecaf01dbc8374</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>LOG_0014</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>PROP_0010</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>481998</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Studio - 76 (Dureuil)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>INT_0001</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>9</v>
+      </c>
+      <c r="O18" t="n">
+        <v>21</v>
+      </c>
+      <c r="P18" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>210</v>
+      </c>
+      <c r="R18" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="S18" t="n">
+        <v>29</v>
+      </c>
+      <c r="T18" t="n">
+        <v>261</v>
+      </c>
+      <c r="U18" t="n">
+        <v>51</v>
+      </c>
+      <c r="V18" t="n">
+        <v>210</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>MEN-2026-05-004</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MEN-2026-05-005</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>d37f34810f1ff454</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>LOG_0008</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>480140</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>T3 - 18 cugnaux (David)</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>INT_0001</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
+      </c>
+      <c r="O19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>175</v>
+      </c>
+      <c r="R19" t="n">
+        <v>35</v>
+      </c>
+      <c r="S19" t="n">
+        <v>55</v>
+      </c>
+      <c r="T19" t="n">
+        <v>275</v>
+      </c>
+      <c r="U19" t="n">
+        <v>100</v>
+      </c>
+      <c r="V19" t="n">
+        <v>175</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>MEN-2026-05-005</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MEN-2026-11-001</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>c6135d3ffa0f8eb8</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>LOG_0008</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>480140</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>T3 - 18 cugnaux (David)</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>INT_0002</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Kheira</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>3</v>
+      </c>
+      <c r="P20" t="n">
+        <v>10</v>
+      </c>
+      <c r="S20" t="n">
+        <v>55</v>
+      </c>
+      <c r="T20" t="n">
+        <v>165</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>MEN-2026-11-001</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MEN-2026-11-002</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>df40be8224d307c7</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>LOG_0003</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>PROP_0003</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>485104</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>T2 - 65 (Gabriel)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>INT_0002</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Kheira</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>10</v>
+      </c>
+      <c r="S21" t="n">
+        <v>39</v>
+      </c>
+      <c r="T21" t="n">
+        <v>39</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>MEN-2026-11-002</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
         </is>
       </c>
     </row>
@@ -1916,7 +4741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2128,9 +4953,2912 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>← PQ Q8 : MASTER filtré statut_controle=VALIDE ET type_intervenant=INTERNE</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MEN-2026-03-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>412a76157796c535</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>LOG_0008</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>480140</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>T3 - 18 cugnaux (David)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>INT_0001</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>6</v>
+      </c>
+      <c r="O2" t="n">
+        <v>20</v>
+      </c>
+      <c r="P2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>200</v>
+      </c>
+      <c r="R2" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="S2" t="n">
+        <v>55</v>
+      </c>
+      <c r="T2" t="n">
+        <v>330</v>
+      </c>
+      <c r="U2" t="n">
+        <v>130</v>
+      </c>
+      <c r="V2" t="n">
+        <v>200</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>MEN-2026-03-001</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MEN-2026-03-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>10fe24845310699b</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>LOG_0014</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>PROP_0010</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>481998</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Studio - 76 (Dureuil)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>INT_0001</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>60</v>
+      </c>
+      <c r="R3" t="n">
+        <v>20</v>
+      </c>
+      <c r="S3" t="n">
+        <v>29</v>
+      </c>
+      <c r="T3" t="n">
+        <v>87</v>
+      </c>
+      <c r="U3" t="n">
+        <v>27</v>
+      </c>
+      <c r="V3" t="n">
+        <v>60</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>MEN-2026-03-002</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MEN-2026-03-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>cd99c4ebea0ad575</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>LOG_0010</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>480142</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Studio - St Pierre (florane)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>INT_0001</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>8</v>
+      </c>
+      <c r="P4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>80</v>
+      </c>
+      <c r="R4" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="S4" t="n">
+        <v>29</v>
+      </c>
+      <c r="T4" t="n">
+        <v>87</v>
+      </c>
+      <c r="U4" t="n">
+        <v>7</v>
+      </c>
+      <c r="V4" t="n">
+        <v>80</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>MEN-2026-03-003</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MEN-2026-03-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>fdc6efca63ff5d45</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>LOG_0005</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>493047</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Studio - 96 (Florane)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>INT_0002</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Kheira</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>8</v>
+      </c>
+      <c r="O5" t="n">
+        <v>24</v>
+      </c>
+      <c r="P5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>240</v>
+      </c>
+      <c r="R5" t="n">
+        <v>30</v>
+      </c>
+      <c r="S5" t="n">
+        <v>29</v>
+      </c>
+      <c r="T5" t="n">
+        <v>232</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-8</v>
+      </c>
+      <c r="V5" t="n">
+        <v>240</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>MEN-2026-03-004</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MEN-2026-03-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>67ea9a859d63810e</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>LOG_0001</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PROP_0001</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>482204</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Studio - 46 (Didier )</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>INT_0002</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Kheira</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>25</v>
+      </c>
+      <c r="P6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>250</v>
+      </c>
+      <c r="R6" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="S6" t="n">
+        <v>29</v>
+      </c>
+      <c r="T6" t="n">
+        <v>232</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-18</v>
+      </c>
+      <c r="V6" t="n">
+        <v>250</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>MEN-2026-03-005</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-001</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>86d918eabec2ad65</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>LOG_0005</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>493047</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Studio - 96 (Florane)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>INT_0002</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Kheira</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>18</v>
+      </c>
+      <c r="P7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>180</v>
+      </c>
+      <c r="R7" t="n">
+        <v>30</v>
+      </c>
+      <c r="S7" t="n">
+        <v>29</v>
+      </c>
+      <c r="T7" t="n">
+        <v>174</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="V7" t="n">
+        <v>180</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-001</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-002</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>cb042425a5d3261c</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>LOG_0015</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>PROP_0011</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>482378</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Studio - 97 (Maryline)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>INT_0002</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Kheira</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>15</v>
+      </c>
+      <c r="P8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>150</v>
+      </c>
+      <c r="R8" t="n">
+        <v>30</v>
+      </c>
+      <c r="S8" t="n">
+        <v>29</v>
+      </c>
+      <c r="T8" t="n">
+        <v>145</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>150</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-002</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-003</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>70877dd74a01ae66</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>LOG_0014</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>PROP_0010</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>481998</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Studio - 76 (Dureuil)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>INT_0002</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Kheira</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>30</v>
+      </c>
+      <c r="R9" t="n">
+        <v>30</v>
+      </c>
+      <c r="S9" t="n">
+        <v>29</v>
+      </c>
+      <c r="T9" t="n">
+        <v>29</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>30</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-003</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-004</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3f65a1e12ee25da3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>LOG_0001</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>PROP_0001</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>482204</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Studio - 46 (Didier )</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>INT_0002</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Kheira</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>8</v>
+      </c>
+      <c r="O10" t="n">
+        <v>28</v>
+      </c>
+      <c r="P10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>280</v>
+      </c>
+      <c r="R10" t="n">
+        <v>35</v>
+      </c>
+      <c r="S10" t="n">
+        <v>29</v>
+      </c>
+      <c r="T10" t="n">
+        <v>232</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-48</v>
+      </c>
+      <c r="V10" t="n">
+        <v>280</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-004</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-005</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>df44e2430ab62ba1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>LOG_0006</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PROP_0006</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>487144</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Studio - Puits vert (Caroline)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>INT_0001</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>30</v>
+      </c>
+      <c r="R11" t="n">
+        <v>30</v>
+      </c>
+      <c r="S11" t="n">
+        <v>29</v>
+      </c>
+      <c r="T11" t="n">
+        <v>29</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>30</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-005</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-006</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>34d6b9535638fb15</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>LOG_0010</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>480142</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Studio - St Pierre (florane)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>INT_0001</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>40</v>
+      </c>
+      <c r="R12" t="n">
+        <v>40</v>
+      </c>
+      <c r="S12" t="n">
+        <v>29</v>
+      </c>
+      <c r="T12" t="n">
+        <v>29</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-11</v>
+      </c>
+      <c r="V12" t="n">
+        <v>40</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-006</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-007</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>042de8d6d554973f</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>LOG_0014</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>PROP_0010</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>481998</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Studio - 76 (Dureuil)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>INT_0001</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>9</v>
+      </c>
+      <c r="P13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>90</v>
+      </c>
+      <c r="R13" t="n">
+        <v>30</v>
+      </c>
+      <c r="S13" t="n">
+        <v>29</v>
+      </c>
+      <c r="T13" t="n">
+        <v>87</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="V13" t="n">
+        <v>90</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-007</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-008</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>c73eb58dc740ec04</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>LOG_0008</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>480140</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>T3 - 18 cugnaux (David)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>INT_0001</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>26</v>
+      </c>
+      <c r="P14" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>260</v>
+      </c>
+      <c r="R14" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="S14" t="n">
+        <v>55</v>
+      </c>
+      <c r="T14" t="n">
+        <v>385</v>
+      </c>
+      <c r="U14" t="n">
+        <v>125</v>
+      </c>
+      <c r="V14" t="n">
+        <v>260</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>MEN-2026-04-008</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MEN-2026-05-001</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7bd60d4dec036460</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>LOG_0015</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>PROP_0011</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>482378</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Studio - 97 (Maryline)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>INT_0002</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Kheira</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>4</v>
+      </c>
+      <c r="O15" t="n">
+        <v>11</v>
+      </c>
+      <c r="P15" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>110</v>
+      </c>
+      <c r="R15" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>29</v>
+      </c>
+      <c r="T15" t="n">
+        <v>116</v>
+      </c>
+      <c r="U15" t="n">
+        <v>6</v>
+      </c>
+      <c r="V15" t="n">
+        <v>110</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>MEN-2026-05-001</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MEN-2026-05-002</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>fd2b6b839bff2bc2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>LOG_0001</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>PROP_0001</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>482204</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Studio - 46 (Didier )</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>INT_0002</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Kheira</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>9</v>
+      </c>
+      <c r="O16" t="n">
+        <v>31</v>
+      </c>
+      <c r="P16" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>310</v>
+      </c>
+      <c r="R16" t="n">
+        <v>34.44</v>
+      </c>
+      <c r="S16" t="n">
+        <v>29</v>
+      </c>
+      <c r="T16" t="n">
+        <v>261</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-49</v>
+      </c>
+      <c r="V16" t="n">
+        <v>310</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>MEN-2026-05-002</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MEN-2026-05-003</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>503757d156fb07a0</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>LOG_0005</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>493047</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Studio - 96 (Florane)</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>INT_0002</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Kheira</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>16</v>
+      </c>
+      <c r="P17" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>160</v>
+      </c>
+      <c r="R17" t="n">
+        <v>32</v>
+      </c>
+      <c r="S17" t="n">
+        <v>29</v>
+      </c>
+      <c r="T17" t="n">
+        <v>145</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-15</v>
+      </c>
+      <c r="V17" t="n">
+        <v>160</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>MEN-2026-05-003</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MEN-2026-05-004</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2ffecaf01dbc8374</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>LOG_0014</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>PROP_0010</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>481998</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Studio - 76 (Dureuil)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>INT_0001</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>9</v>
+      </c>
+      <c r="O18" t="n">
+        <v>21</v>
+      </c>
+      <c r="P18" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>210</v>
+      </c>
+      <c r="R18" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="S18" t="n">
+        <v>29</v>
+      </c>
+      <c r="T18" t="n">
+        <v>261</v>
+      </c>
+      <c r="U18" t="n">
+        <v>51</v>
+      </c>
+      <c r="V18" t="n">
+        <v>210</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>MEN-2026-05-004</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MEN-2026-05-005</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>d37f34810f1ff454</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>LOG_0008</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>480140</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>T3 - 18 cugnaux (David)</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>INT_0001</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Imène</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
+      </c>
+      <c r="O19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>175</v>
+      </c>
+      <c r="R19" t="n">
+        <v>35</v>
+      </c>
+      <c r="S19" t="n">
+        <v>55</v>
+      </c>
+      <c r="T19" t="n">
+        <v>275</v>
+      </c>
+      <c r="U19" t="n">
+        <v>100</v>
+      </c>
+      <c r="V19" t="n">
+        <v>175</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>MEN-2026-05-005</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MEN-2026-11-001</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>c6135d3ffa0f8eb8</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>LOG_0008</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>480140</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>T3 - 18 cugnaux (David)</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>INT_0002</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Kheira</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>3</v>
+      </c>
+      <c r="P20" t="n">
+        <v>10</v>
+      </c>
+      <c r="S20" t="n">
+        <v>55</v>
+      </c>
+      <c r="T20" t="n">
+        <v>165</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>MEN-2026-11-001</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MEN-2026-11-002</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>df40be8224d307c7</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>LOG_0003</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>PROP_0003</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>485104</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>T2 - 65 (Gabriel)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>INT_0002</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Kheira</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>INTERNE</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>MENAGE_STANDARD</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>10</v>
+      </c>
+      <c r="S21" t="n">
+        <v>39</v>
+      </c>
+      <c r="T21" t="n">
+        <v>39</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>TYPE_FLUX_013</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>CHARGE</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>VALIDE</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>lot6b</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>SOURCE_RAW</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>MEN-2026-11-002</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>2026-06-18T11:22:24</t>
         </is>
       </c>
     </row>

--- a/02_DONNEES_NORMALISEES/menages/M04_MENAGES_PowerQuery.xlsx
+++ b/02_DONNEES_NORMALISEES/menages/M04_MENAGES_PowerQuery.xlsx
@@ -1963,7 +1963,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -6859,7 +6859,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>2026-06-18T11:22:24</t>
+          <t>2026-06-18T11:33:09</t>
         </is>
       </c>
     </row>

--- a/02_DONNEES_NORMALISEES/menages/M04_MENAGES_PowerQuery.xlsx
+++ b/02_DONNEES_NORMALISEES/menages/M04_MENAGES_PowerQuery.xlsx
@@ -1963,7 +1963,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -6859,7 +6859,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>2026-06-18T11:33:09</t>
+          <t>2026-06-18T12:10:45</t>
         </is>
       </c>
     </row>

--- a/02_DONNEES_NORMALISEES/menages/M04_MENAGES_PowerQuery.xlsx
+++ b/02_DONNEES_NORMALISEES/menages/M04_MENAGES_PowerQuery.xlsx
@@ -8346,7 +8346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -8583,9 +8583,10 @@
           <t>cout_execution_total</t>
         </is>
       </c>
-      <c r="B24" s="15">
-        <f> nb_heures × taux_horaire_intervenant</f>
-        <v/>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>'= nb_heures × taux_horaire_intervenant</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -8594,9 +8595,10 @@
           <t>cout_standard_total_ligne</t>
         </is>
       </c>
-      <c r="B25" s="15">
-        <f> nb_menages × cout_standard  [BASE PONDÉRATION — non comptable]</f>
-        <v/>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>'= nb_menages × cout_standard  [BASE PONDÉRATION — non comptable]</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -8605,9 +8607,10 @@
           <t>ecart_main_oeuvre_vs_standard</t>
         </is>
       </c>
-      <c r="B26" s="15">
-        <f> cout_standard − cout_execution_unitaire  (positif = favorable)</f>
-        <v/>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>'= cout_standard − cout_execution_unitaire  (positif = favorable)</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -8739,6 +8742,20 @@
       <c r="B40" s="15" t="inlineStr">
         <is>
           <t>total_execution = cout_execution_total (colonne distincte, étape 10bis). Aucun doublon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NOTE (audit 2026-06-18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>M04 alimenté par script déterministe lot6b depuis Google Sheet (REF_Sources_Systeme SRC_011). 'PowerQuery' = nom historique, Power Query non utilisé.</t>
         </is>
       </c>
     </row>
